--- a/output/upload/S00027_1230_장애인전용_곰두리보장보험_무배당.xlsx
+++ b/output/upload/S00027_1230_장애인전용_곰두리보장보험_무배당.xlsx
@@ -2611,17 +2611,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -2702,17 +2694,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -2793,17 +2777,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -2884,17 +2860,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -2975,17 +2943,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -3066,17 +3026,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -3157,17 +3109,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -3248,17 +3192,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -3338,16 +3274,8 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3391,16 +3319,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3444,16 +3364,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3497,16 +3409,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3550,16 +3454,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3603,16 +3499,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3656,16 +3544,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3709,16 +3589,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3762,16 +3634,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3815,16 +3679,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3868,16 +3724,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3921,16 +3769,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>5200018</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_1230_장애인전용_곰두리보장보험_무배당.xlsx
+++ b/output/upload/S00027_1230_장애인전용_곰두리보장보험_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3454,8 +3706,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3499,8 +3774,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3544,8 +3842,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3589,8 +3910,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3634,8 +3978,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3679,8 +4046,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3724,8 +4114,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3769,8 +4182,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1230040</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_1230_장애인전용_곰두리보장보험_무배당.xlsx
+++ b/output/upload/S00027_1230_장애인전용_곰두리보장보험_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>123040</t>
+          <t>1230040</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">

--- a/output/upload/S00027_1230_장애인전용_곰두리보장보험_무배당.xlsx
+++ b/output/upload/S00027_1230_장애인전용_곰두리보장보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:AW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3879,12 +3879,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4105,145 +4105,9 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O24" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>20</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>20</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>20</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>20</v>
-      </c>
-      <c r="O26" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_1230_장애인전용_곰두리보장보험_무배당.xlsx
+++ b/output/upload/S00027_1230_장애인전용_곰두리보장보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW24"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3743,12 +3743,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3811,29 +3811,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>N10</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
       <c r="L20" t="n">
+        <v>20</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
         <v>10</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>20</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3969,145 +3969,9 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O22" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>20</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>15</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1230040</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>한화생명 장애인전용 곰두리보장보험 무배당</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>20</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>20</v>
-      </c>
-      <c r="O24" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
